--- a/Design/Excel/ET/Datas/Game/Scene.xlsx
+++ b/Design/Excel/ET/Datas/Game/Scene.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
   <si>
     <t>##var</t>
   </si>
@@ -78,18 +78,6 @@
   </si>
   <si>
     <t>背景音乐编号</t>
-  </si>
-  <si>
-    <t>Menu</t>
-  </si>
-  <si>
-    <t>菜单场景</t>
-  </si>
-  <si>
-    <t>Main</t>
-  </si>
-  <si>
-    <t>战斗场景</t>
   </si>
 </sst>
 </file>
@@ -1135,38 +1123,18 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="B4" s="3">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="3">
-        <v>1</v>
-      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="B5" s="3">
-        <v>2</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="3">
-        <v>2</v>
-      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:6">
       <c r="F6" s="3"/>
